--- a/bd/producto.xlsx
+++ b/bd/producto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,110 +446,6 @@
         <is>
           <t>id_categoria</t>
         </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>imagen_url</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>eliminado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Camiseta mallada</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>YO SOY TU PADRE</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>165777</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>img/producto_1.jpg</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Camisetaaaa</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Damn</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>61763</v>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>img/producto_2.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Yuval</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>kllklk</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>img/producto_3.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/bd/producto.xlsx
+++ b/bd/producto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,110 @@
         <is>
           <t>id_categoria</t>
         </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>imagen_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>eliminado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Camiseta mallada</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>YO SOY TU PADRE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>165777</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>img/producto_1.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camisetaaaa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Damn</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>61763</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>img/producto_2.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Yuval</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>kllklk</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>img/producto_3.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/bd/producto.xlsx
+++ b/bd/producto.xlsx
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>165777</v>
+        <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61763</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -531,14 +531,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kllklk</t>
+          <t>puro de corazon</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -548,8 +548,8 @@
           <t>img/producto_3.jpg</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
+      <c r="H4" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/bd/producto.xlsx
+++ b/bd/producto.xlsx
@@ -486,7 +486,9 @@
           <t>img/producto_1.jpg</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -516,7 +518,7 @@
           <t>img/producto_2.jpg</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -538,7 +540,7 @@
         <v>300</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>

--- a/bd/producto.xlsx
+++ b/bd/producto.xlsx
@@ -476,7 +476,7 @@
         <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -508,7 +508,7 @@
         <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/bd/producto.xlsx
+++ b/bd/producto.xlsx
@@ -476,7 +476,7 @@
         <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
